--- a/content-pipeline/inputs/book04/b04_ch09_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch09_final.xlsx
@@ -539,10 +539,10 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>三上 ：活力鼓令擂臺賽 （第二十六頁）
-今天，我們代表學校參加了活力鼓令擂臺賽。比賽可謂是高手雲集。最大的有六十多歲的長者，最小的是 只有三四歲的孩童，當然，還有各間學校的代表隊。
-「隆咚隆咚鏘！」比賽開始了，我們穿着紅色和藍色兩種傳統服裝，邁着整齊的步伐走上舞臺，按照各自的位置站好，隨着領鼓的一聲令下，我們揮舞起手中的鼓棍開始表演。首先表演了指定的曲目〈滾核桃〉和〈牛鬥虎〉，同學們久經訓練，早已經不會緊張，今天的表現尤其振奮人心。我們各個神采奕奕，打起鼓來神氣十足，贏得了臺下熱烈的掌聲。接下來我們還表演了自己編排的曲目〈舞動校園〉，由於節奏歡快而有氣勢，我們得到了很高的評分。 之後是一位小童上場，他雖然年紀小，但是表情輕鬆，打起鼓來十分有魄力，無論是造型、節奏還是表情都非常到位。 我們不由得被他身上散發出的那股初生之犢不怕虎的勁頭所打動，對他報以一陣陣喝彩。
-最後，我們獲得了最佳創作獎，大家都非常開心。這次擂臺賽展現了選手們的活力、熱情和專業，讓人深受感染，又能夠跟各間學校，各個年齡段的隊伍進行較量，讓我們鍛煉了膽量，開闊了視野，受益匪淺。比賽結束了，我的心情還十分激動，我會繼續努力，期待今後能夠參加「未來鼓王爭霸賽」。</t>
+          <t>三上 ：活力鼓令擂台賽 （第二十六頁）
+今天，我們代表學校參加了活力鼓令擂台賽。比賽可謂是高手雲集。最大的有六十多歲的長者，最小的是 只有三四歲的孩童，當然，還有各間學校的代表隊。
+「隆咚隆咚鏘！」比賽開始了，我們穿着紅色和藍色兩種傳統服裝，邁着整齊的步伐走上舞台，按照各自的位置站好，隨着領鼓的一聲令下，我們揮舞起手中的鼓棍開始表演。首先表演了指定的曲目〈滾核桃〉和〈牛鬥虎〉，同學們久經訓練，早已經不會緊張，今天的表現尤其振奮人心。我們各個神采奕奕，打起鼓來神氣十足，贏得了台下熱烈的掌聲。接下來我們還表演了自己編排的曲目〈舞動校園〉，由於節奏歡快而有氣勢，我們得到了很高的評分。 之後是一位小童上場，他雖然年紀小，但是表情輕鬆，打起鼓來十分有魄力，無論是造型、節奏還是表情都非常到位。 我們不由得被他身上散發出的那股初生之犢不怕虎的勁頭所打動，對他報以一陣陣喝彩。
+最後，我們獲得了最佳創作獎，大家都非常開心。這次擂台賽展現了選手們的活力、熱情和專業，讓人深受感染，又能夠跟各間學校，各個年齡段的隊伍進行較量，讓我們鍛煉了膽量，開闊了視野，受益匪淺。比賽結束了，我的心情還十分激動，我會繼續努力，期待今後能夠參加「未來鼓王爭霸賽」。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>擂臺賽</t>
+          <t>擂台賽</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
